--- a/stories/arbres/ATOM-VIV.ANI.002-02.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara s'assoit sur le tapis avec maman. Elles ouvrent un livre d'animaux. Une page : un chat, une chatte, un chaton. Maman dit : trois noms de la famille. Sara répète : chat, chatte, chaton. Autre page : un chien, une chienne, un chiot. Sara dit les trois noms. Encore : un coq, une poule, un poussin. Sara pose le doigt sur le poussin. Maman dit : le petit, c'est le poussin. Sara sourit. Trois noms, chaque fois.</t>
+          <t>Sara s'assoit sur le tapis avec maman. Elles ouvrent un livre d'animaux. Une page : un chat, une chatte, un chaton. Trois noms de la famille. Sara répète : chat, chatte, chaton. Autre page : un chien, une chienne, un chiot. Sara dit les trois noms. Encore : un coq, une poule, un poussin. Sara pose le doigt sur le poussin. Le petit, c'est le poussin. Sara sourit. Trois noms, chaque fois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara s'assoit sur le tapis avec maman. Elles ouvrent un livre d'animaux. Une page : un chat, une chatte, un chaton.
+maman|Trois noms de la famille.
+narrateur|Sara répète : chat, chatte, chaton. Autre page : un chien, une chienne, un chiot. Sara dit les trois noms. Encore : un coq, une poule, un poussin. Sara pose le doigt sur le poussin.
+maman|Le petit, c'est le poussin.
+narrateur|Sara sourit. Trois noms, chaque fois.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a dit les trois noms. Chat, chatte, chaton. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman ferme le livre. Sara range le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-02.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Sara sourit. Trois noms, chaque fois.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Sara a dit les trois noms. Chat, chatte, chaton. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Maman ferme le livre. Sara range le coussin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.002-02.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sara dit les trois noms du livre</t>
+          <t>Les bêtes du livre</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut voir dehors les trois bêtes de son livre. Une page est déchirée ; ils la lissent. Coq, poule et poussin picorent vraiment dans la cour.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara s'assoit sur le tapis avec maman. Elles ouvrent un livre d'animaux. Une page : un chat, une chatte, un chaton. Trois noms de la famille. Sara répète : chat, chatte, chaton. Autre page : un chien, une chienne, un chiot. Sara dit les trois noms. Encore : un coq, une poule, un poussin. Sara pose le doigt sur le poussin. Le petit, c'est le poussin. Sara sourit. Trois noms, chaque fois.</t>
+          <t>Une tache jaune glisse sur la page ouverte. Elle s'arrête sur la crête du coq. La table sent encore la confiture. Un peu de sucre colle au bois. Amir vit ici, avec maman. Le livre d'images est trop grand pour ses genoux. Maman, ils sont où, les vrais ? Les bêtes du livre ? Le coq, la poule, le poussin. On peut aller les voir dehors. En ce moment, Amir tourne une page. Le papier râpe un peu sous son pouce. Un coin se lève, tout fin, tout blanc. Oh. Elle est déchirée. On la lisse ensemble ? Maman pose sa main à côté de la sienne. Ils recollent le coin, tout doucement. Le coq du livre redevient entier. Il est réparé. Merci, Amir. Tu as été très doux avec la page. Tu veux encore le livre, ou la cour ? La cour. Les vrais. Ils laissent le livre ouvert sur la table. La tache de soleil reste sur le coq. Maman ouvre la porte vers la basse-cour. L'air sent le grain et la terre chaude. Un grillage vibre un peu au vent. Amir marche près de maman, sans courir. Près de l'abreuvoir, un coq secoue sa crête. Le coq du livre ! Oui. C'est le coq. Une poule rousse picore juste derrière. La poule aussi. Tu la vois bien ? Oui. Un poussin jaune trottine entre les pattes. Le poussin ! Coq, poule, poussin. Trois noms de la famille. Amir s'accroupit près du grillage. Le poussin picore une miette de son ombre. Ils sont dehors, maman. Comme dans le livre. Sauf que ceux-là respirent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara s'assoit sur le tapis avec maman. Elles ouvrent un livre d'animaux. Une page : un chat, une chatte, un chaton. Maman dit : &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms de la famille. Sara répète : chat, chatte, chaton. Autre page : un chien, une chienne, un chiot. Sara dit les trois noms. Encore : un coq, une poule, un poussin. Sara pose le doigt sur le poussin. Maman dit : le petit, c'est le poussin. Sara sourit. Trois noms, chaque fois.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une tache jaune glisse sur la page ouverte. Elle s'arrête sur la crête du coq. La table sent encore la confiture. Un peu de sucre colle au bois. Amir vit ici, avec maman. Le livre d'images est trop grand pour ses genoux. Maman, ils sont où, les vrais ? Les bêtes du livre ? Le coq, la poule, le poussin. On peut aller les voir dehors. En ce moment, Amir tourne une page. Le papier râpe un peu sous son pouce. Un coin se lève, tout fin, tout blanc. Oh. Elle est déchirée. On la lisse ensemble ? Maman pose sa main à côté de la sienne. Ils recollent le coin, tout doucement. Le coq du livre redevient entier. Il est réparé. Merci, Amir. Tu as été très doux avec la page. Tu veux encore le livre, ou la cour ? La cour. Les vrais. Ils laissent le livre ouvert sur la table. La tache de soleil reste sur le coq. Maman ouvre la porte vers la basse-cour. L'air sent le grain et la terre chaude. Un grillage vibre un peu au vent. Amir marche près de maman, sans courir. Près de l'abreuvoir, un coq secoue sa crête. Le coq du livre ! Oui. C'est le coq. Une poule rousse picore juste derrière. La poule aussi. Tu la vois bien ? Oui. Un poussin jaune trottine entre les pattes. Le poussin ! Coq, poule, poussin. Trois noms de la famille. Amir s'accroupit près du grillage. Le poussin picore une miette de son ombre. Ils sont dehors, maman. Comme dans le livre. Sauf que ceux-là respirent.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara s'assoit sur le tapis avec maman. Elles ouvrent un livre d'animaux. Une page : un chat, une chatte, un chaton.
+          <t>narrateur|Une tache jaune glisse sur la page ouverte.
+narrateur|Elle s'arrête sur la crête du coq.
+narrateur|La table sent encore la confiture.
+narrateur|Un peu de sucre colle au bois.
+narrateur|Amir vit ici, avec maman.
+narrateur|Le livre d'images est trop grand pour ses genoux.
+enfant-m|Maman, ils sont où, les vrais ?
+maman|Les bêtes du livre ?
+enfant-m|Le coq, la poule, le poussin.
+maman|On peut aller les voir dehors.
+narrateur|En ce moment, Amir tourne une page.
+narrateur|Le papier râpe un peu sous son pouce.
+narrateur|Un coin se lève, tout fin, tout blanc.
+enfant-m|Oh.
+enfant-m|Elle est déchirée.
+maman|On la lisse ensemble ?
+narrateur|Maman pose sa main à côté de la sienne.
+narrateur|Ils recollent le coin, tout doucement.
+narrateur|Le coq du livre redevient entier.
+enfant-m|Il est réparé.
+maman|Merci, Amir.
+maman|Tu as été très doux avec la page.
+maman|Tu veux encore le livre, ou la cour ?
+enfant-m|La cour.
+enfant-m|Les vrais.
+narrateur|Ils laissent le livre ouvert sur la table.
+narrateur|La tache de soleil reste sur le coq.
+narrateur|Maman ouvre la porte vers la basse-cour.
+narrateur|L'air sent le grain et la terre chaude.
+narrateur|Un grillage vibre un peu au vent.
+narrateur|Amir marche près de maman, sans courir.
+narrateur|Près de l'abreuvoir, un coq secoue sa crête.
+enfant-m|Le coq du livre !
+maman|Oui.
+maman|C'est le coq.
+narrateur|Une poule rousse picore juste derrière.
+enfant-m|La poule aussi.
+maman|Tu la vois bien ?
+enfant-m|Oui.
+narrateur|Un poussin jaune trottine entre les pattes.
+enfant-m|Le poussin !
+maman|Coq, poule, poussin.
 maman|Trois noms de la famille.
-narrateur|Sara répète : chat, chatte, chaton. Autre page : un chien, une chienne, un chiot. Sara dit les trois noms. Encore : un coq, une poule, un poussin. Sara pose le doigt sur le poussin.
-maman|Le petit, c'est le poussin.
-narrateur|Sara sourit. Trois noms, chaque fois.</t>
+narrateur|Amir s'accroupit près du grillage.
+narrateur|Le poussin picore une miette de son ombre.
+enfant-m|Ils sont dehors, maman.
+maman|Comme dans le livre.
+maman|Sauf que ceux-là respirent.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,27 +1403,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Les trois bêtes du livre, elles sont où ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Les trois bêtes du livre, elles sont où ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le coq, la poule, et le petit. Quel est le petit ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Le coq, la poule, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>poussin</t>
+          <t>dehors</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>poussin | le poussin | le petit | chaton</t>
+          <t>dehors | dans la cour | à la basse-cour | la cour</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1438,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Les trois noms de la famille. Le petit, c'est qui ?</t>
+          <t>Elles sont dehors. Où sont les trois bêtes ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1425,14 +1480,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1559,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Les trois bêtes du livre, elles sont où ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1586,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara a dit les trois noms. Chat, chatte, chaton. Coq, poule, poussin.</t>
+          <t>Le coq chante une note courte. La poule rentre un peu sous son aile le poussin. Il est tout petit. Oui. C'est le petit de la poule. Tu te souviens de la page ? On l'a lissée. Un peu de poussière dore encore le grillage. On reste regarder ? Encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara a dit les &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Chat, chatte, chaton. Coq, poule, poussin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le coq chante une note courte. La poule rentre un peu sous son aile le poussin. Il est tout petit. Oui. C'est le petit de la poule. Tu te souviens de la page ? On l'a lissée. Un peu de poussière dore encore le grillage. On reste regarder ? Encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1654,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1730,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara a dit les trois noms. Chat, chatte, chaton. Coq, poule, poussin.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le coq chante une note courte.
+narrateur|La poule rentre un peu sous son aile le poussin.
+enfant-m|Il est tout petit.
+maman|Oui.
+maman|C'est le petit de la poule.
+maman|Tu te souviens de la page ?
+enfant-m|On l'a lissée.
+narrateur|Un peu de poussière dore encore le grillage.
+maman|On reste regarder ?
+enfant-m|Encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1766,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman ferme le livre. Sara range le coussin.</t>
+          <t>Ils rentrent vers la cuisine. Le livre attend, ouvert, sur la table. La page lissée tient encore. Le coq du papier est entier. Et le coq dehors a chanté. Tu as vu les trois ? Coq, poule, poussin. Amir pose un doigt sur le papier réparé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman ferme le livre. Sara range le coussin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils rentrent vers la cuisine. Le livre attend, ouvert, sur la table. La page lissée tient encore. Le coq du papier est entier. Et le coq dehors a chanté. Tu as vu les trois ? Coq, poule, poussin. Amir pose un doigt sur le papier réparé.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1834,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1902,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman ferme le livre. Sara range le coussin.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils rentrent vers la cuisine.
+narrateur|Le livre attend, ouvert, sur la table.
+narrateur|La page lissée tient encore.
+enfant-m|Le coq du papier est entier.
+maman|Et le coq dehors a chanté.
+maman|Tu as vu les trois ?
+enfant-m|Coq, poule, poussin.
+narrateur|Amir pose un doigt sur le papier réparé.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1936,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Ils picorent vraiment. Dehors, dans la lumière. Les trois bêtes picorent dans la poussière d'or.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils picorent vraiment. Dehors, dans la lumière. Les trois bêtes picorent dans la poussière d'or.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1936,7 +2004,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2076,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Ils picorent vraiment.
+maman|Dehors, dans la lumière.
+narrateur|Les trois bêtes picorent dans la poussière d'or.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2137,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-02.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>cuisine, livre d'images, puis basse-cour</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
